--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B63D527-266F-4FB2-A17F-453DAB23CC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB149A39-FE10-453A-A6EE-9DB9D8356199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="420" windowWidth="25440" windowHeight="15270" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
+    <workbookView xWindow="-23340" yWindow="2865" windowWidth="21600" windowHeight="11295" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -708,7 +708,7 @@
         <v>3397</v>
       </c>
       <c r="C20" s="1">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="D20" s="2">
         <v>46126</v>
@@ -721,7 +721,9 @@
       <c r="B21" s="1">
         <v>2790.5</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>22000</v>
+      </c>
       <c r="D21" s="2">
         <v>46127</v>
       </c>
@@ -733,7 +735,9 @@
       <c r="B22" s="1">
         <v>930</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="C22" s="1">
+        <v>24000</v>
+      </c>
       <c r="D22" s="2">
         <v>46128</v>
       </c>
@@ -745,7 +749,9 @@
       <c r="B23" s="1">
         <v>7595</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="1">
+        <v>26000</v>
+      </c>
       <c r="D23" s="2">
         <v>46129</v>
       </c>
@@ -757,7 +763,9 @@
       <c r="B24" s="1">
         <v>8848</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1">
+        <v>28000</v>
+      </c>
       <c r="D24" s="2">
         <v>46130</v>
       </c>
@@ -769,7 +777,9 @@
       <c r="B25" s="1">
         <v>3654</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1">
+        <v>30000</v>
+      </c>
       <c r="D25" s="2">
         <v>46131</v>
       </c>
@@ -781,7 +791,9 @@
       <c r="B26" s="1">
         <v>5427.2</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1">
+        <v>30000</v>
+      </c>
       <c r="D26" s="2">
         <v>46132</v>
       </c>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB149A39-FE10-453A-A6EE-9DB9D8356199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D9531-B292-4DF1-8D48-740A73A70037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23340" yWindow="2865" windowWidth="21600" windowHeight="11295" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
+    <workbookView xWindow="-25320" yWindow="420" windowWidth="25440" windowHeight="15270" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -736,7 +736,7 @@
         <v>930</v>
       </c>
       <c r="C22" s="1">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="D22" s="2">
         <v>46128</v>
@@ -750,7 +750,7 @@
         <v>7595</v>
       </c>
       <c r="C23" s="1">
-        <v>26000</v>
+        <v>10000</v>
       </c>
       <c r="D23" s="2">
         <v>46129</v>
@@ -764,7 +764,7 @@
         <v>8848</v>
       </c>
       <c r="C24" s="1">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="D24" s="2">
         <v>46130</v>
@@ -778,7 +778,7 @@
         <v>3654</v>
       </c>
       <c r="C25" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="D25" s="2">
         <v>46131</v>
@@ -792,7 +792,7 @@
         <v>5427.2</v>
       </c>
       <c r="C26" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="D26" s="2">
         <v>46132</v>
@@ -805,7 +805,9 @@
       <c r="B27" s="1">
         <v>5587.6</v>
       </c>
-      <c r="C27" s="1"/>
+      <c r="C27" s="1">
+        <v>20000</v>
+      </c>
       <c r="D27" s="2">
         <v>46133</v>
       </c>
@@ -817,7 +819,9 @@
       <c r="B28" s="1">
         <v>9528</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>20000</v>
+      </c>
       <c r="D28" s="2">
         <v>46134</v>
       </c>
@@ -829,7 +833,9 @@
       <c r="B29" s="1">
         <v>3334.5</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1">
+        <v>25000</v>
+      </c>
       <c r="D29" s="2">
         <v>46135</v>
       </c>
@@ -841,7 +847,9 @@
       <c r="B30" s="1">
         <v>8031</v>
       </c>
-      <c r="C30" s="1"/>
+      <c r="C30" s="1">
+        <v>25000</v>
+      </c>
       <c r="D30" s="2">
         <v>46136</v>
       </c>
@@ -853,7 +861,9 @@
       <c r="B31" s="1">
         <v>4511</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1">
+        <v>30000</v>
+      </c>
       <c r="D31" s="2">
         <v>46137</v>
       </c>
@@ -865,7 +875,9 @@
       <c r="B32" s="1">
         <v>5728</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <v>30000</v>
+      </c>
       <c r="D32" s="2">
         <v>46138</v>
       </c>
@@ -877,7 +889,9 @@
       <c r="B33" s="1">
         <v>4425</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>30000</v>
+      </c>
       <c r="D33" s="2">
         <v>46139</v>
       </c>
@@ -889,7 +903,9 @@
       <c r="B34" s="1">
         <v>6056.7</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>35000</v>
+      </c>
       <c r="D34" s="2">
         <v>46140</v>
       </c>
@@ -901,7 +917,9 @@
       <c r="B35" s="1">
         <v>9565.5</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1">
+        <v>35000</v>
+      </c>
       <c r="D35" s="2">
         <v>46141</v>
       </c>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D9531-B292-4DF1-8D48-740A73A70037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44161F10-34FC-4AF8-9CF9-84B5B9B7B2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="420" windowWidth="25440" windowHeight="15270" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Days Remaining Until Aidiladha</t>
   </si>
@@ -44,19 +44,36 @@
     <t>Current Sale Last Year</t>
   </si>
   <si>
-    <t>Daily Target</t>
+    <t>Date</t>
   </si>
   <si>
-    <t>Date</t>
+    <t>Daily Sales Target</t>
+  </si>
+  <si>
+    <t>Daily Sales Forecast</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -71,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -79,21 +96,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{963A6FCA-BE1B-4A2B-B7DC-15C8DC357101}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{41DDD867-B056-43E4-8A4B-9A3430163321}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -425,658 +476,789 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3A8BE5-470C-4EA6-AEB1-948F2C421233}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>61</v>
       </c>
       <c r="B2" s="1">
         <v>755</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46108</v>
+      </c>
+      <c r="E2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="2">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>60</v>
       </c>
       <c r="B3" s="1">
         <v>822.6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46109</v>
+      </c>
+      <c r="E3" s="3">
         <v>0</v>
       </c>
-      <c r="D3" s="2">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>1080</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46110</v>
+      </c>
+      <c r="E4" s="3">
         <v>0</v>
       </c>
-      <c r="D4" s="2">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>58</v>
       </c>
       <c r="B5" s="1">
         <v>1492</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46111</v>
+      </c>
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="2">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>57</v>
       </c>
       <c r="B6" s="1">
         <v>520</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46112</v>
+      </c>
+      <c r="E6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="2">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>56</v>
       </c>
       <c r="B7" s="1">
         <v>480</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46113</v>
+      </c>
+      <c r="E7" s="3">
         <v>0</v>
       </c>
-      <c r="D7" s="2">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>55</v>
       </c>
       <c r="B8" s="1">
         <v>261</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
+        <v>6600</v>
+      </c>
+      <c r="D8" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E8" s="5">
         <v>10000</v>
       </c>
-      <c r="D8" s="2">
-        <v>46114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>54</v>
       </c>
       <c r="B9" s="1">
         <v>623.6</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46115</v>
+      </c>
+      <c r="E9" s="5">
         <v>10000</v>
       </c>
-      <c r="D9" s="2">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>53</v>
       </c>
       <c r="B10" s="1">
         <v>2318.1999999999998</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46116</v>
+      </c>
+      <c r="E10" s="5">
         <v>14000</v>
       </c>
-      <c r="D10" s="2">
-        <v>46116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>52</v>
       </c>
       <c r="B11" s="1">
         <v>1144.5</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46117</v>
+      </c>
+      <c r="E11" s="5">
         <v>14000</v>
       </c>
-      <c r="D11" s="2">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>51</v>
       </c>
       <c r="B12" s="1">
         <v>317</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46118</v>
+      </c>
+      <c r="E12" s="5">
         <v>16000</v>
       </c>
-      <c r="D12" s="2">
-        <v>46118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>50</v>
       </c>
       <c r="B13" s="1">
         <v>2314.6999999999998</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D13" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E13" s="5">
         <v>16000</v>
       </c>
-      <c r="D13" s="2">
-        <v>46119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>49</v>
       </c>
       <c r="B14" s="1">
         <v>2087</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D14" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E14" s="5">
         <v>18000</v>
       </c>
-      <c r="D14" s="2">
-        <v>46120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>48</v>
       </c>
       <c r="B15" s="1">
         <v>110</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="6">
+        <v>12572</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46121</v>
+      </c>
+      <c r="E15" s="5">
         <v>18000</v>
       </c>
-      <c r="D15" s="2">
-        <v>46121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>47</v>
       </c>
       <c r="B16" s="1">
         <v>3602.73</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46122</v>
+      </c>
+      <c r="E16" s="5">
         <v>20000</v>
       </c>
-      <c r="D16" s="2">
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46</v>
       </c>
       <c r="B17" s="1">
         <v>3290.2</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46123</v>
+      </c>
+      <c r="E17" s="5">
         <v>20000</v>
       </c>
-      <c r="D17" s="2">
-        <v>46123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>45</v>
       </c>
       <c r="B18" s="1">
         <v>3662.5</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D18" s="4">
+        <v>46124</v>
+      </c>
+      <c r="E18" s="5">
         <v>20000</v>
       </c>
-      <c r="D18" s="2">
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>44</v>
       </c>
       <c r="B19" s="1">
         <v>19311</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46125</v>
+      </c>
+      <c r="E19" s="5">
         <v>20000</v>
       </c>
-      <c r="D19" s="2">
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>43</v>
       </c>
       <c r="B20" s="1">
         <v>3397</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D20" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E20" s="5">
         <v>22000</v>
       </c>
-      <c r="D20" s="2">
-        <v>46126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>42</v>
       </c>
       <c r="B21" s="1">
         <v>2790.5</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D21" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E21" s="5">
         <v>22000</v>
       </c>
-      <c r="D21" s="2">
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>41</v>
       </c>
       <c r="B22" s="1">
         <v>930</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
+        <v>11100</v>
+      </c>
+      <c r="D22" s="4">
+        <v>46128</v>
+      </c>
+      <c r="E22" s="5">
         <v>10000</v>
       </c>
-      <c r="D22" s="2">
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>40</v>
       </c>
       <c r="B23" s="1">
         <v>7595</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D23" s="4">
+        <v>46129</v>
+      </c>
+      <c r="E23" s="5">
         <v>10000</v>
       </c>
-      <c r="D23" s="2">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>39</v>
       </c>
       <c r="B24" s="1">
         <v>8848</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46130</v>
+      </c>
+      <c r="E24" s="5">
         <v>15000</v>
       </c>
-      <c r="D24" s="2">
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>38</v>
       </c>
       <c r="B25" s="1">
         <v>3654</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E25" s="5">
         <v>15000</v>
       </c>
-      <c r="D25" s="2">
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>37</v>
       </c>
       <c r="B26" s="1">
         <v>5427.2</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D26" s="4">
+        <v>46132</v>
+      </c>
+      <c r="E26" s="5">
         <v>15000</v>
       </c>
-      <c r="D26" s="2">
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>36</v>
       </c>
       <c r="B27" s="1">
         <v>5587.6</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46133</v>
+      </c>
+      <c r="E27" s="5">
         <v>20000</v>
       </c>
-      <c r="D27" s="2">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>35</v>
       </c>
       <c r="B28" s="1">
         <v>9528</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D28" s="4">
+        <v>46134</v>
+      </c>
+      <c r="E28" s="5">
         <v>20000</v>
       </c>
-      <c r="D28" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>34</v>
       </c>
       <c r="B29" s="1">
         <v>3334.5</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="6">
+        <v>16000</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46135</v>
+      </c>
+      <c r="E29" s="5">
         <v>25000</v>
       </c>
-      <c r="D29" s="2">
-        <v>46135</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>33</v>
       </c>
       <c r="B30" s="1">
         <v>8031</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D30" s="4">
+        <v>46136</v>
+      </c>
+      <c r="E30" s="5">
         <v>25000</v>
       </c>
-      <c r="D30" s="2">
-        <v>46136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>32</v>
       </c>
       <c r="B31" s="1">
         <v>4511</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D31" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E31" s="5">
         <v>30000</v>
       </c>
-      <c r="D31" s="2">
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1">
         <v>5728</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D32" s="4">
+        <v>46138</v>
+      </c>
+      <c r="E32" s="5">
         <v>30000</v>
       </c>
-      <c r="D32" s="2">
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>30</v>
       </c>
       <c r="B33" s="1">
         <v>4425</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D33" s="4">
+        <v>46139</v>
+      </c>
+      <c r="E33" s="5">
         <v>30000</v>
       </c>
-      <c r="D33" s="2">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>29</v>
       </c>
       <c r="B34" s="1">
         <v>6056.7</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D34" s="4">
+        <v>46140</v>
+      </c>
+      <c r="E34" s="5">
         <v>35000</v>
       </c>
-      <c r="D34" s="2">
-        <v>46140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>28</v>
       </c>
       <c r="B35" s="1">
         <v>9565.5</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D35" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E35" s="5">
         <v>35000</v>
       </c>
-      <c r="D35" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>27</v>
       </c>
       <c r="B36" s="1">
         <v>11649.5</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="2">
+      <c r="C36" s="6">
+        <v>20000</v>
+      </c>
+      <c r="D36" s="4">
         <v>46142</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>26</v>
       </c>
       <c r="B37" s="1">
         <v>7653.6</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="2">
+      <c r="C37" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D37" s="4">
         <v>46143</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>25</v>
       </c>
       <c r="B38" s="1">
         <v>6303.8</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="2">
+      <c r="C38" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D38" s="4">
         <v>46144</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>24</v>
       </c>
       <c r="B39" s="1">
         <v>10529.4</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="2">
+      <c r="C39" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D39" s="4">
         <v>46145</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>23</v>
       </c>
       <c r="B40" s="1">
         <v>13391.4</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="2">
+      <c r="C40" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D40" s="4">
         <v>46146</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>22</v>
       </c>
       <c r="B41" s="1">
         <v>11934</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="2">
+      <c r="C41" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D41" s="4">
         <v>46147</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>21</v>
       </c>
       <c r="B42" s="1">
         <v>19388.8</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="2">
+      <c r="C42" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D42" s="4">
         <v>46148</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>20</v>
       </c>
       <c r="B43" s="1">
         <v>14699.52</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="2">
+      <c r="C43" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D43" s="4">
         <v>46149</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>19</v>
       </c>
       <c r="B44" s="1">
         <v>10322</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="2">
+      <c r="C44" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D44" s="4">
         <v>46150</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>18</v>
       </c>
       <c r="B45" s="1">
         <v>9212.1</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="2">
+      <c r="C45" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D45" s="4">
         <v>46151</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>17</v>
       </c>
       <c r="B46" s="1">
         <v>14127.5</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="2">
+      <c r="C46" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D46" s="4">
         <v>46152</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>16</v>
       </c>
       <c r="B47" s="1">
         <v>18729.75</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="2">
+      <c r="C47" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D47" s="4">
         <v>46153</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>15</v>
       </c>
       <c r="B48" s="1">
         <v>21760.82</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="2">
+      <c r="C48" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D48" s="4">
         <v>46154</v>
       </c>
     </row>
@@ -1087,8 +1269,10 @@
       <c r="B49" s="1">
         <v>23098</v>
       </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="2">
+      <c r="C49" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D49" s="4">
         <v>46155</v>
       </c>
     </row>
@@ -1099,8 +1283,10 @@
       <c r="B50" s="1">
         <v>19807.400000000001</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="2">
+      <c r="C50" s="6">
+        <v>35000</v>
+      </c>
+      <c r="D50" s="4">
         <v>46156</v>
       </c>
     </row>
@@ -1111,8 +1297,10 @@
       <c r="B51" s="1">
         <v>20345.7</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="2">
+      <c r="C51" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D51" s="4">
         <v>46157</v>
       </c>
     </row>
@@ -1123,8 +1311,10 @@
       <c r="B52" s="1">
         <v>22587</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="2">
+      <c r="C52" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D52" s="4">
         <v>46158</v>
       </c>
     </row>
@@ -1135,8 +1325,10 @@
       <c r="B53" s="1">
         <v>25684</v>
       </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="2">
+      <c r="C53" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D53" s="4">
         <v>46159</v>
       </c>
     </row>
@@ -1147,8 +1339,10 @@
       <c r="B54" s="1">
         <v>22745.5</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="2">
+      <c r="C54" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D54" s="4">
         <v>46160</v>
       </c>
     </row>
@@ -1159,8 +1353,10 @@
       <c r="B55" s="1">
         <v>30446</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="2">
+      <c r="C55" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D55" s="4">
         <v>46161</v>
       </c>
     </row>
@@ -1171,8 +1367,10 @@
       <c r="B56" s="1">
         <v>44606.35</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="2">
+      <c r="C56" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D56" s="4">
         <v>46162</v>
       </c>
     </row>
@@ -1183,8 +1381,10 @@
       <c r="B57" s="1">
         <v>46852.85</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="2">
+      <c r="C57" s="6">
+        <v>60000</v>
+      </c>
+      <c r="D57" s="4">
         <v>46163</v>
       </c>
     </row>
@@ -1195,8 +1395,10 @@
       <c r="B58" s="1">
         <v>50162.95</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="2">
+      <c r="C58" s="6">
+        <v>70000</v>
+      </c>
+      <c r="D58" s="4">
         <v>46164</v>
       </c>
     </row>
@@ -1207,8 +1409,10 @@
       <c r="B59" s="1">
         <v>45366.9</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="2">
+      <c r="C59" s="6">
+        <v>70000</v>
+      </c>
+      <c r="D59" s="4">
         <v>46165</v>
       </c>
     </row>
@@ -1219,8 +1423,10 @@
       <c r="B60" s="1">
         <v>47609.599999999999</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="2">
+      <c r="C60" s="6">
+        <v>70000</v>
+      </c>
+      <c r="D60" s="4">
         <v>46166</v>
       </c>
     </row>
@@ -1231,8 +1437,10 @@
       <c r="B61" s="1">
         <v>58847.75</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="2">
+      <c r="C61" s="6">
+        <v>70000</v>
+      </c>
+      <c r="D61" s="4">
         <v>46167</v>
       </c>
     </row>
@@ -1243,8 +1451,10 @@
       <c r="B62" s="1">
         <v>96236.2</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="2">
+      <c r="C62" s="6">
+        <v>70000</v>
+      </c>
+      <c r="D62" s="4">
         <v>46168</v>
       </c>
     </row>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44161F10-34FC-4AF8-9CF9-84B5B9B7B2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E3321-0F14-4B8A-B0B0-951972535AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="420" windowWidth="25440" windowHeight="15270" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,26 +119,26 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -481,7 +481,7 @@
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -492,7 +492,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -509,13 +509,13 @@
       <c r="B2" s="1">
         <v>755</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>6600</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>46108</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -526,13 +526,13 @@
       <c r="B3" s="1">
         <v>822.6</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>6600</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>46109</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -543,13 +543,13 @@
       <c r="B4" s="1">
         <v>1080</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>6600</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>46110</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -560,13 +560,13 @@
       <c r="B5" s="1">
         <v>1492</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>6600</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>46111</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -577,13 +577,13 @@
       <c r="B6" s="1">
         <v>520</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>6600</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>46112</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -594,13 +594,13 @@
       <c r="B7" s="1">
         <v>480</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>6600</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>46113</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -611,13 +611,13 @@
       <c r="B8" s="1">
         <v>261</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>6600</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>46114</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>10000</v>
       </c>
     </row>
@@ -628,13 +628,13 @@
       <c r="B9" s="1">
         <v>623.6</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>12572</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>46115</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>10000</v>
       </c>
     </row>
@@ -645,13 +645,13 @@
       <c r="B10" s="1">
         <v>2318.1999999999998</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>12572</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>46116</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>14000</v>
       </c>
     </row>
@@ -662,13 +662,13 @@
       <c r="B11" s="1">
         <v>1144.5</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>12572</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>46117</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>14000</v>
       </c>
     </row>
@@ -679,13 +679,13 @@
       <c r="B12" s="1">
         <v>317</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>12572</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>46118</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>16000</v>
       </c>
     </row>
@@ -696,13 +696,13 @@
       <c r="B13" s="1">
         <v>2314.6999999999998</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>12572</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>46119</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>16000</v>
       </c>
     </row>
@@ -713,13 +713,13 @@
       <c r="B14" s="1">
         <v>2087</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>12572</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>46120</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>18000</v>
       </c>
     </row>
@@ -730,13 +730,13 @@
       <c r="B15" s="1">
         <v>110</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>12572</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>46121</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>18000</v>
       </c>
     </row>
@@ -747,13 +747,13 @@
       <c r="B16" s="1">
         <v>3602.73</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>11100</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>46122</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -764,13 +764,13 @@
       <c r="B17" s="1">
         <v>3290.2</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>11100</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>46123</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -781,13 +781,13 @@
       <c r="B18" s="1">
         <v>3662.5</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>11100</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>46124</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -798,13 +798,13 @@
       <c r="B19" s="1">
         <v>19311</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>11100</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>46125</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -815,13 +815,13 @@
       <c r="B20" s="1">
         <v>3397</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>11100</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>46126</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>22000</v>
       </c>
     </row>
@@ -832,13 +832,13 @@
       <c r="B21" s="1">
         <v>2790.5</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>11100</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>46127</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>22000</v>
       </c>
     </row>
@@ -849,13 +849,13 @@
       <c r="B22" s="1">
         <v>930</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>11100</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>46128</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>10000</v>
       </c>
     </row>
@@ -866,13 +866,13 @@
       <c r="B23" s="1">
         <v>7595</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>16000</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>46129</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>10000</v>
       </c>
     </row>
@@ -883,13 +883,13 @@
       <c r="B24" s="1">
         <v>8848</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>16000</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>46130</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>15000</v>
       </c>
     </row>
@@ -900,13 +900,13 @@
       <c r="B25" s="1">
         <v>3654</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>16000</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>46131</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>15000</v>
       </c>
     </row>
@@ -917,13 +917,13 @@
       <c r="B26" s="1">
         <v>5427.2</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>16000</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>46132</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>15000</v>
       </c>
     </row>
@@ -934,13 +934,13 @@
       <c r="B27" s="1">
         <v>5587.6</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>16000</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>46133</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -951,13 +951,13 @@
       <c r="B28" s="1">
         <v>9528</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>16000</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>46134</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>20000</v>
       </c>
     </row>
@@ -968,13 +968,13 @@
       <c r="B29" s="1">
         <v>3334.5</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>16000</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>46135</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>25000</v>
       </c>
     </row>
@@ -985,13 +985,13 @@
       <c r="B30" s="1">
         <v>8031</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>20000</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>46136</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>25000</v>
       </c>
     </row>
@@ -1002,13 +1002,13 @@
       <c r="B31" s="1">
         <v>4511</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>20000</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>46137</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>30000</v>
       </c>
     </row>
@@ -1019,13 +1019,13 @@
       <c r="B32" s="1">
         <v>5728</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>20000</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>46138</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>30000</v>
       </c>
     </row>
@@ -1036,13 +1036,13 @@
       <c r="B33" s="1">
         <v>4425</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>20000</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>46139</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>30000</v>
       </c>
     </row>
@@ -1053,13 +1053,13 @@
       <c r="B34" s="1">
         <v>6056.7</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>20000</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>46140</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>35000</v>
       </c>
     </row>
@@ -1070,13 +1070,13 @@
       <c r="B35" s="1">
         <v>9565.5</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>20000</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>46141</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>35000</v>
       </c>
     </row>
@@ -1087,11 +1087,14 @@
       <c r="B36" s="1">
         <v>11649.5</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>20000</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>46142</v>
+      </c>
+      <c r="E36" s="4">
+        <v>35000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1101,11 +1104,14 @@
       <c r="B37" s="1">
         <v>7653.6</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>30000</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>46143</v>
+      </c>
+      <c r="E37" s="4">
+        <v>35000</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1115,11 +1121,14 @@
       <c r="B38" s="1">
         <v>6303.8</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>30000</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>46144</v>
+      </c>
+      <c r="E38" s="4">
+        <v>35000</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1129,11 +1138,14 @@
       <c r="B39" s="1">
         <v>10529.4</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>30000</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>46145</v>
+      </c>
+      <c r="E39" s="4">
+        <v>35000</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1143,11 +1155,14 @@
       <c r="B40" s="1">
         <v>13391.4</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>30000</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>46146</v>
+      </c>
+      <c r="E40" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1157,11 +1172,14 @@
       <c r="B41" s="1">
         <v>11934</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>30000</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>46147</v>
+      </c>
+      <c r="E41" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1171,11 +1189,14 @@
       <c r="B42" s="1">
         <v>19388.8</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>30000</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>46148</v>
+      </c>
+      <c r="E42" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1185,11 +1206,14 @@
       <c r="B43" s="1">
         <v>14699.52</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>30000</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>46149</v>
+      </c>
+      <c r="E43" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1199,11 +1223,14 @@
       <c r="B44" s="1">
         <v>10322</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>35000</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>46150</v>
+      </c>
+      <c r="E44" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,11 +1240,14 @@
       <c r="B45" s="1">
         <v>9212.1</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>35000</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="3">
         <v>46151</v>
+      </c>
+      <c r="E45" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1227,11 +1257,14 @@
       <c r="B46" s="1">
         <v>14127.5</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>35000</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="3">
         <v>46152</v>
+      </c>
+      <c r="E46" s="7">
+        <v>45000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1241,10 +1274,10 @@
       <c r="B47" s="1">
         <v>18729.75</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>35000</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>46153</v>
       </c>
     </row>
@@ -1255,10 +1288,10 @@
       <c r="B48" s="1">
         <v>21760.82</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>35000</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>46154</v>
       </c>
     </row>
@@ -1269,10 +1302,10 @@
       <c r="B49" s="1">
         <v>23098</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>35000</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>46155</v>
       </c>
     </row>
@@ -1283,10 +1316,10 @@
       <c r="B50" s="1">
         <v>19807.400000000001</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>35000</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>46156</v>
       </c>
     </row>
@@ -1297,10 +1330,10 @@
       <c r="B51" s="1">
         <v>20345.7</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>60000</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>46157</v>
       </c>
     </row>
@@ -1311,10 +1344,10 @@
       <c r="B52" s="1">
         <v>22587</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>60000</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>46158</v>
       </c>
     </row>
@@ -1325,10 +1358,10 @@
       <c r="B53" s="1">
         <v>25684</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>60000</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="3">
         <v>46159</v>
       </c>
     </row>
@@ -1339,10 +1372,10 @@
       <c r="B54" s="1">
         <v>22745.5</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>60000</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>46160</v>
       </c>
     </row>
@@ -1353,10 +1386,10 @@
       <c r="B55" s="1">
         <v>30446</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>60000</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="3">
         <v>46161</v>
       </c>
     </row>
@@ -1367,10 +1400,10 @@
       <c r="B56" s="1">
         <v>44606.35</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>60000</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>46162</v>
       </c>
     </row>
@@ -1381,10 +1414,10 @@
       <c r="B57" s="1">
         <v>46852.85</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>60000</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="3">
         <v>46163</v>
       </c>
     </row>
@@ -1395,10 +1428,10 @@
       <c r="B58" s="1">
         <v>50162.95</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>70000</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>46164</v>
       </c>
     </row>
@@ -1409,10 +1442,10 @@
       <c r="B59" s="1">
         <v>45366.9</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>70000</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="3">
         <v>46165</v>
       </c>
     </row>
@@ -1423,10 +1456,10 @@
       <c r="B60" s="1">
         <v>47609.599999999999</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>70000</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="3">
         <v>46166</v>
       </c>
     </row>
@@ -1437,10 +1470,10 @@
       <c r="B61" s="1">
         <v>58847.75</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>70000</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="3">
         <v>46167</v>
       </c>
     </row>
@@ -1451,10 +1484,10 @@
       <c r="B62" s="1">
         <v>96236.2</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>70000</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>46168</v>
       </c>
     </row>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233E3321-0F14-4B8A-B0B0-951972535AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC63C972-E03A-4526-A4CA-6BF2103AEDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -117,7 +117,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,9 +136,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1161,8 +1158,8 @@
       <c r="D40" s="3">
         <v>46146</v>
       </c>
-      <c r="E40" s="7">
-        <v>45000</v>
+      <c r="E40" s="4">
+        <v>38000</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1178,8 +1175,8 @@
       <c r="D41" s="3">
         <v>46147</v>
       </c>
-      <c r="E41" s="7">
-        <v>45000</v>
+      <c r="E41" s="4">
+        <v>40000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1195,8 +1192,8 @@
       <c r="D42" s="3">
         <v>46148</v>
       </c>
-      <c r="E42" s="7">
-        <v>45000</v>
+      <c r="E42" s="4">
+        <v>43000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1212,8 +1209,8 @@
       <c r="D43" s="3">
         <v>46149</v>
       </c>
-      <c r="E43" s="7">
-        <v>45000</v>
+      <c r="E43" s="4">
+        <v>46000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1229,8 +1226,8 @@
       <c r="D44" s="3">
         <v>46150</v>
       </c>
-      <c r="E44" s="7">
-        <v>45000</v>
+      <c r="E44" s="4">
+        <v>49000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1246,8 +1243,8 @@
       <c r="D45" s="3">
         <v>46151</v>
       </c>
-      <c r="E45" s="7">
-        <v>45000</v>
+      <c r="E45" s="4">
+        <v>55000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1263,8 +1260,8 @@
       <c r="D46" s="3">
         <v>46152</v>
       </c>
-      <c r="E46" s="7">
-        <v>45000</v>
+      <c r="E46" s="4">
+        <v>50000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC63C972-E03A-4526-A4CA-6BF2103AEDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135E4CA4-B64D-4BF0-BE05-EF9E6D58F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -1176,7 +1176,7 @@
         <v>46147</v>
       </c>
       <c r="E41" s="4">
-        <v>40000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,7 +1193,7 @@
         <v>46148</v>
       </c>
       <c r="E42" s="4">
-        <v>43000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135E4CA4-B64D-4BF0-BE05-EF9E6D58F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84CE815-ED2F-4A59-B45D-9631E57380E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -117,7 +117,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +136,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1277,6 +1280,9 @@
       <c r="D47" s="3">
         <v>46153</v>
       </c>
+      <c r="E47" s="7">
+        <v>56000</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
@@ -1291,8 +1297,11 @@
       <c r="D48" s="3">
         <v>46154</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>14</v>
       </c>
@@ -1305,8 +1314,11 @@
       <c r="D49" s="3">
         <v>46155</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>13</v>
       </c>
@@ -1319,8 +1331,11 @@
       <c r="D50" s="3">
         <v>46156</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>12</v>
       </c>
@@ -1333,8 +1348,11 @@
       <c r="D51" s="3">
         <v>46157</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>11</v>
       </c>
@@ -1347,8 +1365,11 @@
       <c r="D52" s="3">
         <v>46158</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>10</v>
       </c>
@@ -1361,8 +1382,11 @@
       <c r="D53" s="3">
         <v>46159</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="7">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>9</v>
       </c>
@@ -1375,8 +1399,11 @@
       <c r="D54" s="3">
         <v>46160</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>8</v>
       </c>
@@ -1389,8 +1416,11 @@
       <c r="D55" s="3">
         <v>46161</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>7</v>
       </c>
@@ -1403,8 +1433,11 @@
       <c r="D56" s="3">
         <v>46162</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -1417,8 +1450,11 @@
       <c r="D57" s="3">
         <v>46163</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>5</v>
       </c>
@@ -1431,8 +1467,11 @@
       <c r="D58" s="3">
         <v>46164</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>4</v>
       </c>
@@ -1445,8 +1484,11 @@
       <c r="D59" s="3">
         <v>46165</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>3</v>
       </c>
@@ -1459,8 +1501,11 @@
       <c r="D60" s="3">
         <v>46166</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="7">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>2</v>
       </c>
@@ -1473,8 +1518,11 @@
       <c r="D61" s="3">
         <v>46167</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -1486,6 +1534,9 @@
       </c>
       <c r="D62" s="3">
         <v>46168</v>
+      </c>
+      <c r="E62" s="7">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SalmanNorSalehan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84CE815-ED2F-4A59-B45D-9631E57380E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EABA8B-A2C9-4CD1-9CFF-4C5D3B385F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -117,7 +117,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,9 +136,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1280,7 +1277,7 @@
       <c r="D47" s="3">
         <v>46153</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1297,7 +1294,7 @@
       <c r="D48" s="3">
         <v>46154</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1314,7 +1311,7 @@
       <c r="D49" s="3">
         <v>46155</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1331,7 +1328,7 @@
       <c r="D50" s="3">
         <v>46156</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1348,7 +1345,7 @@
       <c r="D51" s="3">
         <v>46157</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1365,7 +1362,7 @@
       <c r="D52" s="3">
         <v>46158</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1382,7 +1379,7 @@
       <c r="D53" s="3">
         <v>46159</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="4">
         <v>56000</v>
       </c>
     </row>
@@ -1399,7 +1396,7 @@
       <c r="D54" s="3">
         <v>46160</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="4">
         <v>65000</v>
       </c>
     </row>
@@ -1416,7 +1413,7 @@
       <c r="D55" s="3">
         <v>46161</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="4">
         <v>65000</v>
       </c>
     </row>
@@ -1433,7 +1430,7 @@
       <c r="D56" s="3">
         <v>46162</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="4">
         <v>65000</v>
       </c>
     </row>
@@ -1450,7 +1447,7 @@
       <c r="D57" s="3">
         <v>46163</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="4">
         <v>65000</v>
       </c>
     </row>
@@ -1467,7 +1464,7 @@
       <c r="D58" s="3">
         <v>46164</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="4">
         <v>65000</v>
       </c>
     </row>
@@ -1484,8 +1481,8 @@
       <c r="D59" s="3">
         <v>46165</v>
       </c>
-      <c r="E59" s="7">
-        <v>65000</v>
+      <c r="E59" s="4">
+        <v>85000</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1501,8 +1498,8 @@
       <c r="D60" s="3">
         <v>46166</v>
       </c>
-      <c r="E60" s="7">
-        <v>65000</v>
+      <c r="E60" s="4">
+        <v>85000</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1518,8 +1515,8 @@
       <c r="D61" s="3">
         <v>46167</v>
       </c>
-      <c r="E61" s="7">
-        <v>100000</v>
+      <c r="E61" s="4">
+        <v>90000</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1535,8 +1532,8 @@
       <c r="D62" s="3">
         <v>46168</v>
       </c>
-      <c r="E62" s="7">
-        <v>100000</v>
+      <c r="E62" s="4">
+        <v>90000</v>
       </c>
     </row>
   </sheetData>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SalmanNorSalehan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EABA8B-A2C9-4CD1-9CFF-4C5D3B385F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC79986-49B8-4D9E-BAA8-85ABB8A1D94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B587A664-E792-49AA-8BA6-0492C364E442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA4E7AC-16DE-4DB6-A7F2-CEB6D0BF8997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -518,7 +518,7 @@
         <v>46175</v>
       </c>
       <c r="E3" s="2">
-        <v>12001</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -529,7 +529,7 @@
         <v>46176</v>
       </c>
       <c r="E4" s="2">
-        <v>12002</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -540,7 +540,7 @@
         <v>46177</v>
       </c>
       <c r="E5" s="2">
-        <v>12003</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -551,7 +551,7 @@
         <v>46178</v>
       </c>
       <c r="E6" s="2">
-        <v>12004</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -562,7 +562,7 @@
         <v>46179</v>
       </c>
       <c r="E7" s="2">
-        <v>12005</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>46180</v>
       </c>
       <c r="E8" s="2">
-        <v>12006</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -584,7 +584,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="2">
-        <v>12007</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -595,7 +595,7 @@
         <v>46182</v>
       </c>
       <c r="E10" s="2">
-        <v>12008</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -606,7 +606,7 @@
         <v>46183</v>
       </c>
       <c r="E11" s="2">
-        <v>12009</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -617,7 +617,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="2">
-        <v>12010</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
         <v>46185</v>
       </c>
       <c r="E13" s="2">
-        <v>12011</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -639,7 +639,7 @@
         <v>46186</v>
       </c>
       <c r="E14" s="2">
-        <v>12012</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>46187</v>
       </c>
       <c r="E15" s="2">
-        <v>12013</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -661,7 +661,7 @@
         <v>46188</v>
       </c>
       <c r="E16" s="2">
-        <v>12014</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -672,7 +672,7 @@
         <v>46189</v>
       </c>
       <c r="E17" s="2">
-        <v>12015</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -683,7 +683,7 @@
         <v>46190</v>
       </c>
       <c r="E18" s="2">
-        <v>12016</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -694,7 +694,7 @@
         <v>46191</v>
       </c>
       <c r="E19" s="2">
-        <v>12017</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -705,7 +705,7 @@
         <v>46192</v>
       </c>
       <c r="E20" s="2">
-        <v>12018</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,7 +716,7 @@
         <v>46193</v>
       </c>
       <c r="E21" s="2">
-        <v>12019</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -727,7 +727,7 @@
         <v>46194</v>
       </c>
       <c r="E22" s="2">
-        <v>12020</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -738,7 +738,7 @@
         <v>46195</v>
       </c>
       <c r="E23" s="2">
-        <v>12021</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -749,7 +749,7 @@
         <v>46196</v>
       </c>
       <c r="E24" s="2">
-        <v>12022</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -760,7 +760,7 @@
         <v>46197</v>
       </c>
       <c r="E25" s="2">
-        <v>12023</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -771,7 +771,7 @@
         <v>46198</v>
       </c>
       <c r="E26" s="2">
-        <v>12024</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -782,7 +782,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="2">
-        <v>12025</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -793,7 +793,7 @@
         <v>46200</v>
       </c>
       <c r="E28" s="2">
-        <v>12026</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -804,7 +804,7 @@
         <v>46201</v>
       </c>
       <c r="E29" s="2">
-        <v>12027</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -815,7 +815,7 @@
         <v>46202</v>
       </c>
       <c r="E30" s="2">
-        <v>12028</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -826,7 +826,7 @@
         <v>46203</v>
       </c>
       <c r="E31" s="2">
-        <v>12029</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DBDA9A-3B18-4545-B882-E248F05E0973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42127F2-C42B-4231-9D0B-0CC1A023C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Days Remaining Until Aidiladha</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Current Sale Last Year</t>
   </si>
@@ -473,35 +470,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3A8BE5-470C-4EA6-AEB1-948F2C421233}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>61</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>46108</v>
       </c>
       <c r="B2" s="1">
         <v>755</v>
@@ -509,16 +502,13 @@
       <c r="C2" s="5">
         <v>6600</v>
       </c>
-      <c r="D2" s="3">
-        <v>46108</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>60</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>46109</v>
       </c>
       <c r="B3" s="1">
         <v>822.6</v>
@@ -526,16 +516,13 @@
       <c r="C3" s="5">
         <v>6600</v>
       </c>
-      <c r="D3" s="3">
-        <v>46109</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>59</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>46110</v>
       </c>
       <c r="B4" s="1">
         <v>1080</v>
@@ -543,16 +530,13 @@
       <c r="C4" s="5">
         <v>6600</v>
       </c>
-      <c r="D4" s="3">
-        <v>46110</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>58</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46111</v>
       </c>
       <c r="B5" s="1">
         <v>1492</v>
@@ -560,16 +544,13 @@
       <c r="C5" s="5">
         <v>6600</v>
       </c>
-      <c r="D5" s="3">
-        <v>46111</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>57</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>46112</v>
       </c>
       <c r="B6" s="1">
         <v>520</v>
@@ -577,16 +558,13 @@
       <c r="C6" s="5">
         <v>6600</v>
       </c>
-      <c r="D6" s="3">
-        <v>46112</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>56</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>46113</v>
       </c>
       <c r="B7" s="1">
         <v>480</v>
@@ -594,16 +572,13 @@
       <c r="C7" s="5">
         <v>6600</v>
       </c>
-      <c r="D7" s="3">
-        <v>46113</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>55</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>46114</v>
       </c>
       <c r="B8" s="1">
         <v>261</v>
@@ -611,16 +586,13 @@
       <c r="C8" s="5">
         <v>6600</v>
       </c>
-      <c r="D8" s="3">
-        <v>46114</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>54</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>46115</v>
       </c>
       <c r="B9" s="1">
         <v>623.6</v>
@@ -628,16 +600,13 @@
       <c r="C9" s="5">
         <v>12572</v>
       </c>
-      <c r="D9" s="3">
-        <v>46115</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>53</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>46116</v>
       </c>
       <c r="B10" s="1">
         <v>2318.1999999999998</v>
@@ -645,16 +614,13 @@
       <c r="C10" s="5">
         <v>12572</v>
       </c>
-      <c r="D10" s="3">
-        <v>46116</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="4">
         <v>14000</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>52</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>46117</v>
       </c>
       <c r="B11" s="1">
         <v>1144.5</v>
@@ -662,16 +628,13 @@
       <c r="C11" s="5">
         <v>12572</v>
       </c>
-      <c r="D11" s="3">
-        <v>46117</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="4">
         <v>14000</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>51</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>46118</v>
       </c>
       <c r="B12" s="1">
         <v>317</v>
@@ -679,16 +642,13 @@
       <c r="C12" s="5">
         <v>12572</v>
       </c>
-      <c r="D12" s="3">
-        <v>46118</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="4">
         <v>16000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>50</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>46119</v>
       </c>
       <c r="B13" s="1">
         <v>2314.6999999999998</v>
@@ -696,16 +656,13 @@
       <c r="C13" s="5">
         <v>12572</v>
       </c>
-      <c r="D13" s="3">
-        <v>46119</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="4">
         <v>16000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>49</v>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>46120</v>
       </c>
       <c r="B14" s="1">
         <v>2087</v>
@@ -713,16 +670,13 @@
       <c r="C14" s="5">
         <v>12572</v>
       </c>
-      <c r="D14" s="3">
-        <v>46120</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="4">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>48</v>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>46121</v>
       </c>
       <c r="B15" s="1">
         <v>110</v>
@@ -730,16 +684,13 @@
       <c r="C15" s="5">
         <v>12572</v>
       </c>
-      <c r="D15" s="3">
-        <v>46121</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15" s="4">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>47</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>46122</v>
       </c>
       <c r="B16" s="1">
         <v>3602.73</v>
@@ -747,16 +698,13 @@
       <c r="C16" s="5">
         <v>11100</v>
       </c>
-      <c r="D16" s="3">
-        <v>46122</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>46</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>46123</v>
       </c>
       <c r="B17" s="1">
         <v>3290.2</v>
@@ -764,16 +712,13 @@
       <c r="C17" s="5">
         <v>11100</v>
       </c>
-      <c r="D17" s="3">
-        <v>46123</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>45</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>46124</v>
       </c>
       <c r="B18" s="1">
         <v>3662.5</v>
@@ -781,16 +726,13 @@
       <c r="C18" s="5">
         <v>11100</v>
       </c>
-      <c r="D18" s="3">
-        <v>46124</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>44</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>46125</v>
       </c>
       <c r="B19" s="1">
         <v>19311</v>
@@ -798,16 +740,13 @@
       <c r="C19" s="5">
         <v>11100</v>
       </c>
-      <c r="D19" s="3">
-        <v>46125</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>43</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>46126</v>
       </c>
       <c r="B20" s="1">
         <v>3397</v>
@@ -815,16 +754,13 @@
       <c r="C20" s="5">
         <v>11100</v>
       </c>
-      <c r="D20" s="3">
-        <v>46126</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="4">
         <v>22000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>42</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>46127</v>
       </c>
       <c r="B21" s="1">
         <v>2790.5</v>
@@ -832,16 +768,13 @@
       <c r="C21" s="5">
         <v>11100</v>
       </c>
-      <c r="D21" s="3">
-        <v>46127</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D21" s="4">
         <v>22000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>41</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>46128</v>
       </c>
       <c r="B22" s="1">
         <v>930</v>
@@ -849,16 +782,13 @@
       <c r="C22" s="5">
         <v>11100</v>
       </c>
-      <c r="D22" s="3">
-        <v>46128</v>
-      </c>
-      <c r="E22" s="4">
+      <c r="D22" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>40</v>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>46129</v>
       </c>
       <c r="B23" s="1">
         <v>7595</v>
@@ -866,16 +796,13 @@
       <c r="C23" s="5">
         <v>16000</v>
       </c>
-      <c r="D23" s="3">
-        <v>46129</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="D23" s="4">
         <v>10000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>39</v>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>46130</v>
       </c>
       <c r="B24" s="1">
         <v>8848</v>
@@ -883,16 +810,13 @@
       <c r="C24" s="5">
         <v>16000</v>
       </c>
-      <c r="D24" s="3">
-        <v>46130</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="D24" s="4">
         <v>15000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>38</v>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>46131</v>
       </c>
       <c r="B25" s="1">
         <v>3654</v>
@@ -900,16 +824,13 @@
       <c r="C25" s="5">
         <v>16000</v>
       </c>
-      <c r="D25" s="3">
-        <v>46131</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D25" s="4">
         <v>15000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>37</v>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>46132</v>
       </c>
       <c r="B26" s="1">
         <v>5427.2</v>
@@ -917,16 +838,13 @@
       <c r="C26" s="5">
         <v>16000</v>
       </c>
-      <c r="D26" s="3">
-        <v>46132</v>
-      </c>
-      <c r="E26" s="4">
+      <c r="D26" s="4">
         <v>15000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>36</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>46133</v>
       </c>
       <c r="B27" s="1">
         <v>5587.6</v>
@@ -934,16 +852,13 @@
       <c r="C27" s="5">
         <v>16000</v>
       </c>
-      <c r="D27" s="3">
-        <v>46133</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="D27" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>35</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>46134</v>
       </c>
       <c r="B28" s="1">
         <v>9528</v>
@@ -951,16 +866,13 @@
       <c r="C28" s="5">
         <v>16000</v>
       </c>
-      <c r="D28" s="3">
-        <v>46134</v>
-      </c>
-      <c r="E28" s="4">
+      <c r="D28" s="4">
         <v>20000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>34</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>46135</v>
       </c>
       <c r="B29" s="1">
         <v>3334.5</v>
@@ -968,16 +880,13 @@
       <c r="C29" s="5">
         <v>16000</v>
       </c>
-      <c r="D29" s="3">
-        <v>46135</v>
-      </c>
-      <c r="E29" s="4">
+      <c r="D29" s="4">
         <v>25000</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>33</v>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>46136</v>
       </c>
       <c r="B30" s="1">
         <v>8031</v>
@@ -985,16 +894,13 @@
       <c r="C30" s="5">
         <v>20000</v>
       </c>
-      <c r="D30" s="3">
-        <v>46136</v>
-      </c>
-      <c r="E30" s="4">
+      <c r="D30" s="4">
         <v>25000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>32</v>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>46137</v>
       </c>
       <c r="B31" s="1">
         <v>4511</v>
@@ -1002,16 +908,13 @@
       <c r="C31" s="5">
         <v>20000</v>
       </c>
-      <c r="D31" s="3">
-        <v>46137</v>
-      </c>
-      <c r="E31" s="4">
+      <c r="D31" s="4">
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>31</v>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>46138</v>
       </c>
       <c r="B32" s="1">
         <v>5728</v>
@@ -1019,16 +922,13 @@
       <c r="C32" s="5">
         <v>20000</v>
       </c>
-      <c r="D32" s="3">
-        <v>46138</v>
-      </c>
-      <c r="E32" s="4">
+      <c r="D32" s="4">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>30</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>46139</v>
       </c>
       <c r="B33" s="1">
         <v>4425</v>
@@ -1036,16 +936,13 @@
       <c r="C33" s="5">
         <v>20000</v>
       </c>
-      <c r="D33" s="3">
-        <v>46139</v>
-      </c>
-      <c r="E33" s="4">
+      <c r="D33" s="4">
         <v>30000</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>29</v>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>46140</v>
       </c>
       <c r="B34" s="1">
         <v>6056.7</v>
@@ -1053,16 +950,13 @@
       <c r="C34" s="5">
         <v>20000</v>
       </c>
-      <c r="D34" s="3">
-        <v>46140</v>
-      </c>
-      <c r="E34" s="4">
+      <c r="D34" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>28</v>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>46141</v>
       </c>
       <c r="B35" s="1">
         <v>9565.5</v>
@@ -1070,16 +964,13 @@
       <c r="C35" s="5">
         <v>20000</v>
       </c>
-      <c r="D35" s="3">
-        <v>46141</v>
-      </c>
-      <c r="E35" s="4">
+      <c r="D35" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>27</v>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>46142</v>
       </c>
       <c r="B36" s="1">
         <v>11649.5</v>
@@ -1087,16 +978,13 @@
       <c r="C36" s="5">
         <v>20000</v>
       </c>
-      <c r="D36" s="3">
-        <v>46142</v>
-      </c>
-      <c r="E36" s="4">
+      <c r="D36" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>26</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>46143</v>
       </c>
       <c r="B37" s="1">
         <v>7653.6</v>
@@ -1104,16 +992,13 @@
       <c r="C37" s="5">
         <v>30000</v>
       </c>
-      <c r="D37" s="3">
-        <v>46143</v>
-      </c>
-      <c r="E37" s="4">
+      <c r="D37" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>25</v>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>46144</v>
       </c>
       <c r="B38" s="1">
         <v>6303.8</v>
@@ -1121,16 +1006,13 @@
       <c r="C38" s="5">
         <v>30000</v>
       </c>
-      <c r="D38" s="3">
-        <v>46144</v>
-      </c>
-      <c r="E38" s="4">
+      <c r="D38" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>24</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>46145</v>
       </c>
       <c r="B39" s="1">
         <v>10529.4</v>
@@ -1138,16 +1020,13 @@
       <c r="C39" s="5">
         <v>30000</v>
       </c>
-      <c r="D39" s="3">
-        <v>46145</v>
-      </c>
-      <c r="E39" s="4">
+      <c r="D39" s="4">
         <v>35000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>23</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>46146</v>
       </c>
       <c r="B40" s="1">
         <v>13391.4</v>
@@ -1155,16 +1034,13 @@
       <c r="C40" s="5">
         <v>30000</v>
       </c>
-      <c r="D40" s="3">
-        <v>46146</v>
-      </c>
-      <c r="E40" s="4">
+      <c r="D40" s="4">
         <v>38000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>22</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>46147</v>
       </c>
       <c r="B41" s="1">
         <v>11934</v>
@@ -1172,16 +1048,13 @@
       <c r="C41" s="5">
         <v>30000</v>
       </c>
-      <c r="D41" s="3">
-        <v>46147</v>
-      </c>
-      <c r="E41" s="4">
+      <c r="D41" s="4">
         <v>45000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>21</v>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>46148</v>
       </c>
       <c r="B42" s="1">
         <v>19388.8</v>
@@ -1189,16 +1062,13 @@
       <c r="C42" s="5">
         <v>30000</v>
       </c>
-      <c r="D42" s="3">
-        <v>46148</v>
-      </c>
-      <c r="E42" s="4">
+      <c r="D42" s="4">
         <v>45000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>20</v>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>46149</v>
       </c>
       <c r="B43" s="1">
         <v>14699.52</v>
@@ -1206,16 +1076,13 @@
       <c r="C43" s="5">
         <v>30000</v>
       </c>
-      <c r="D43" s="3">
-        <v>46149</v>
-      </c>
-      <c r="E43" s="4">
+      <c r="D43" s="4">
         <v>46000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>19</v>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>46150</v>
       </c>
       <c r="B44" s="1">
         <v>10322</v>
@@ -1223,16 +1090,13 @@
       <c r="C44" s="5">
         <v>35000</v>
       </c>
-      <c r="D44" s="3">
-        <v>46150</v>
-      </c>
-      <c r="E44" s="4">
+      <c r="D44" s="4">
         <v>49000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>18</v>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>46151</v>
       </c>
       <c r="B45" s="1">
         <v>9212.1</v>
@@ -1240,16 +1104,13 @@
       <c r="C45" s="5">
         <v>35000</v>
       </c>
-      <c r="D45" s="3">
-        <v>46151</v>
-      </c>
-      <c r="E45" s="4">
+      <c r="D45" s="4">
         <v>55000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>17</v>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>46152</v>
       </c>
       <c r="B46" s="1">
         <v>14127.5</v>
@@ -1257,16 +1118,13 @@
       <c r="C46" s="5">
         <v>35000</v>
       </c>
-      <c r="D46" s="3">
-        <v>46152</v>
-      </c>
-      <c r="E46" s="4">
+      <c r="D46" s="4">
         <v>50000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>16</v>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>46153</v>
       </c>
       <c r="B47" s="1">
         <v>18729.75</v>
@@ -1274,16 +1132,13 @@
       <c r="C47" s="5">
         <v>35000</v>
       </c>
-      <c r="D47" s="3">
-        <v>46153</v>
-      </c>
-      <c r="E47" s="4">
+      <c r="D47" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>15</v>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>46154</v>
       </c>
       <c r="B48" s="1">
         <v>21760.82</v>
@@ -1291,16 +1146,13 @@
       <c r="C48" s="5">
         <v>35000</v>
       </c>
-      <c r="D48" s="3">
-        <v>46154</v>
-      </c>
-      <c r="E48" s="4">
+      <c r="D48" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>14</v>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>46155</v>
       </c>
       <c r="B49" s="1">
         <v>23098</v>
@@ -1308,16 +1160,13 @@
       <c r="C49" s="5">
         <v>35000</v>
       </c>
-      <c r="D49" s="3">
-        <v>46155</v>
-      </c>
-      <c r="E49" s="4">
+      <c r="D49" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>13</v>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>46156</v>
       </c>
       <c r="B50" s="1">
         <v>19807.400000000001</v>
@@ -1325,16 +1174,13 @@
       <c r="C50" s="5">
         <v>35000</v>
       </c>
-      <c r="D50" s="3">
-        <v>46156</v>
-      </c>
-      <c r="E50" s="4">
+      <c r="D50" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>12</v>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>46157</v>
       </c>
       <c r="B51" s="1">
         <v>20345.7</v>
@@ -1342,16 +1188,13 @@
       <c r="C51" s="5">
         <v>60000</v>
       </c>
-      <c r="D51" s="3">
-        <v>46157</v>
-      </c>
-      <c r="E51" s="4">
+      <c r="D51" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>11</v>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>46158</v>
       </c>
       <c r="B52" s="1">
         <v>22587</v>
@@ -1359,16 +1202,13 @@
       <c r="C52" s="5">
         <v>60000</v>
       </c>
-      <c r="D52" s="3">
-        <v>46158</v>
-      </c>
-      <c r="E52" s="4">
+      <c r="D52" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>10</v>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>46159</v>
       </c>
       <c r="B53" s="1">
         <v>25684</v>
@@ -1376,16 +1216,13 @@
       <c r="C53" s="5">
         <v>60000</v>
       </c>
-      <c r="D53" s="3">
-        <v>46159</v>
-      </c>
-      <c r="E53" s="4">
+      <c r="D53" s="4">
         <v>56000</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>9</v>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>46160</v>
       </c>
       <c r="B54" s="1">
         <v>22745.5</v>
@@ -1393,16 +1230,13 @@
       <c r="C54" s="5">
         <v>60000</v>
       </c>
-      <c r="D54" s="3">
-        <v>46160</v>
-      </c>
-      <c r="E54" s="4">
+      <c r="D54" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>8</v>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>46161</v>
       </c>
       <c r="B55" s="1">
         <v>30446</v>
@@ -1410,16 +1244,13 @@
       <c r="C55" s="5">
         <v>60000</v>
       </c>
-      <c r="D55" s="3">
-        <v>46161</v>
-      </c>
-      <c r="E55" s="4">
+      <c r="D55" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>7</v>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>46162</v>
       </c>
       <c r="B56" s="1">
         <v>44606.35</v>
@@ -1427,16 +1258,13 @@
       <c r="C56" s="5">
         <v>60000</v>
       </c>
-      <c r="D56" s="3">
-        <v>46162</v>
-      </c>
-      <c r="E56" s="4">
+      <c r="D56" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>6</v>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>46163</v>
       </c>
       <c r="B57" s="1">
         <v>46852.85</v>
@@ -1444,16 +1272,13 @@
       <c r="C57" s="5">
         <v>60000</v>
       </c>
-      <c r="D57" s="3">
-        <v>46163</v>
-      </c>
-      <c r="E57" s="4">
+      <c r="D57" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>5</v>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>46164</v>
       </c>
       <c r="B58" s="1">
         <v>50162.95</v>
@@ -1461,16 +1286,13 @@
       <c r="C58" s="5">
         <v>70000</v>
       </c>
-      <c r="D58" s="3">
-        <v>46164</v>
-      </c>
-      <c r="E58" s="4">
+      <c r="D58" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>4</v>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>46165</v>
       </c>
       <c r="B59" s="1">
         <v>45366.9</v>
@@ -1478,16 +1300,13 @@
       <c r="C59" s="5">
         <v>70000</v>
       </c>
-      <c r="D59" s="3">
-        <v>46165</v>
-      </c>
-      <c r="E59" s="4">
+      <c r="D59" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>3</v>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>46166</v>
       </c>
       <c r="B60" s="1">
         <v>47609.599999999999</v>
@@ -1495,16 +1314,13 @@
       <c r="C60" s="5">
         <v>70000</v>
       </c>
-      <c r="D60" s="3">
-        <v>46166</v>
-      </c>
-      <c r="E60" s="4">
+      <c r="D60" s="4">
         <v>65000</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>2</v>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>46167</v>
       </c>
       <c r="B61" s="1">
         <v>58847.75</v>
@@ -1512,16 +1328,13 @@
       <c r="C61" s="5">
         <v>70000</v>
       </c>
-      <c r="D61" s="3">
-        <v>46167</v>
-      </c>
-      <c r="E61" s="4">
+      <c r="D61" s="4">
         <v>100000</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>1</v>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>46168</v>
       </c>
       <c r="B62" s="1">
         <v>96236.2</v>
@@ -1529,385 +1342,304 @@
       <c r="C62" s="5">
         <v>70000</v>
       </c>
-      <c r="D62" s="3">
-        <v>46168</v>
-      </c>
-      <c r="E62" s="4">
+      <c r="D62" s="4">
         <v>100000</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>0</v>
-      </c>
-      <c r="D63" s="3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>46169</v>
       </c>
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>354</v>
-      </c>
-      <c r="D64" s="3">
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>46170</v>
       </c>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>353</v>
-      </c>
-      <c r="D65" s="3">
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>46171</v>
       </c>
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>352</v>
-      </c>
-      <c r="D66" s="3">
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>46172</v>
       </c>
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>351</v>
-      </c>
-      <c r="D67" s="3">
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>46173</v>
       </c>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>350</v>
-      </c>
-      <c r="D68" s="3">
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>46174</v>
       </c>
-      <c r="E68" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>349</v>
-      </c>
-      <c r="D69" s="3">
+      <c r="D68" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>46175</v>
       </c>
-      <c r="E69" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>348</v>
-      </c>
-      <c r="D70" s="3">
+      <c r="D69" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>46176</v>
       </c>
-      <c r="E70" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>347</v>
-      </c>
-      <c r="D71" s="3">
+      <c r="D70" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>46177</v>
       </c>
-      <c r="E71" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>346</v>
-      </c>
-      <c r="D72" s="3">
+      <c r="D71" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>46178</v>
       </c>
-      <c r="E72" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>345</v>
-      </c>
-      <c r="D73" s="3">
+      <c r="D72" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>46179</v>
       </c>
-      <c r="E73" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>344</v>
-      </c>
-      <c r="D74" s="3">
+      <c r="D73" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>46180</v>
       </c>
-      <c r="E74" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>343</v>
-      </c>
-      <c r="D75" s="3">
+      <c r="D74" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>46181</v>
       </c>
-      <c r="E75" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>342</v>
-      </c>
-      <c r="D76" s="3">
+      <c r="D75" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>46182</v>
       </c>
-      <c r="E76" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>341</v>
-      </c>
-      <c r="D77" s="3">
+      <c r="D76" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>46183</v>
       </c>
-      <c r="E77" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>340</v>
-      </c>
-      <c r="D78" s="3">
+      <c r="D77" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>46184</v>
       </c>
-      <c r="E78" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>339</v>
-      </c>
-      <c r="D79" s="3">
+      <c r="D78" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>46185</v>
       </c>
-      <c r="E79" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>338</v>
-      </c>
-      <c r="D80" s="3">
+      <c r="D79" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>46186</v>
       </c>
-      <c r="E80" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>337</v>
-      </c>
-      <c r="D81" s="3">
+      <c r="D80" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>46187</v>
       </c>
-      <c r="E81" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>336</v>
-      </c>
-      <c r="D82" s="3">
+      <c r="D81" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>46188</v>
       </c>
-      <c r="E82" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>335</v>
-      </c>
-      <c r="D83" s="3">
+      <c r="D82" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>46189</v>
       </c>
-      <c r="E83" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>334</v>
-      </c>
-      <c r="D84" s="3">
+      <c r="D83" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>46190</v>
       </c>
-      <c r="E84" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>333</v>
-      </c>
-      <c r="D85" s="3">
+      <c r="D84" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
         <v>46191</v>
       </c>
-      <c r="E85" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>332</v>
-      </c>
-      <c r="D86" s="3">
+      <c r="D85" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
         <v>46192</v>
       </c>
-      <c r="E86" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>331</v>
-      </c>
-      <c r="D87" s="3">
+      <c r="D86" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
         <v>46193</v>
       </c>
-      <c r="E87" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>330</v>
-      </c>
-      <c r="D88" s="3">
+      <c r="D87" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
         <v>46194</v>
       </c>
-      <c r="E88" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>329</v>
-      </c>
-      <c r="D89" s="3">
+      <c r="D88" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
         <v>46195</v>
       </c>
-      <c r="E89" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>328</v>
-      </c>
-      <c r="D90" s="3">
+      <c r="C89" s="6">
+        <v>11000</v>
+      </c>
+      <c r="D89" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
         <v>46196</v>
       </c>
-      <c r="E90" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>327</v>
-      </c>
-      <c r="D91" s="3">
+      <c r="C90" s="6">
+        <v>11000</v>
+      </c>
+      <c r="D90" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
         <v>46197</v>
       </c>
-      <c r="E91" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>326</v>
-      </c>
-      <c r="D92" s="3">
+      <c r="C91" s="6">
+        <v>12000</v>
+      </c>
+      <c r="D91" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
         <v>46198</v>
       </c>
-      <c r="E92" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>325</v>
-      </c>
-      <c r="D93" s="3">
+      <c r="C92" s="6">
+        <v>15000</v>
+      </c>
+      <c r="D92" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
         <v>46199</v>
       </c>
-      <c r="E93" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>324</v>
-      </c>
-      <c r="D94" s="3">
+      <c r="C93" s="6">
+        <v>17000</v>
+      </c>
+      <c r="D93" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>46200</v>
       </c>
-      <c r="E94" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>323</v>
-      </c>
-      <c r="D95" s="3">
+      <c r="C94" s="6">
+        <v>17500</v>
+      </c>
+      <c r="D94" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>46201</v>
       </c>
-      <c r="E95" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>322</v>
-      </c>
-      <c r="D96" s="3">
+      <c r="C95" s="6">
+        <v>16500</v>
+      </c>
+      <c r="D95" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
         <v>46202</v>
       </c>
-      <c r="E96" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>321</v>
-      </c>
-      <c r="D97" s="3">
+      <c r="C96" s="6">
+        <v>8500</v>
+      </c>
+      <c r="D96" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
         <v>46203</v>
       </c>
-      <c r="E97" s="2">
+      <c r="C97" s="6">
+        <v>8500</v>
+      </c>
+      <c r="D97" s="2">
         <v>12000</v>
       </c>
     </row>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Downloads\Salman\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Documents\Gearevo Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42127F2-C42B-4231-9D0B-0CC1A023C204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5530A-0FD5-4BC2-ACDA-350669EA5BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -470,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3A8BE5-470C-4EA6-AEB1-948F2C421233}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
@@ -1643,6 +1643,502 @@
         <v>12000</v>
       </c>
     </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>46204</v>
+      </c>
+      <c r="C98" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D98" s="6">
+        <v>10326</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>46205</v>
+      </c>
+      <c r="C99" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D99" s="6">
+        <v>10326</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>46206</v>
+      </c>
+      <c r="C100" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D100" s="6">
+        <v>11359</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>46207</v>
+      </c>
+      <c r="C101" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D101" s="6">
+        <v>13424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>46208</v>
+      </c>
+      <c r="C102" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D102" s="6">
+        <v>13424</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>46209</v>
+      </c>
+      <c r="C103" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D103" s="6">
+        <v>10326</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
+        <v>46210</v>
+      </c>
+      <c r="C104" s="6">
+        <v>13571</v>
+      </c>
+      <c r="D104" s="6">
+        <v>25815</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
+        <v>46211</v>
+      </c>
+      <c r="C105" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D105" s="6">
+        <v>11039</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
+        <v>46212</v>
+      </c>
+      <c r="C106" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D106" s="6">
+        <v>11039</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
+        <v>46213</v>
+      </c>
+      <c r="C107" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D107" s="6">
+        <v>12143</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
+        <v>46214</v>
+      </c>
+      <c r="C108" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D108" s="6">
+        <v>14351</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
+        <v>46215</v>
+      </c>
+      <c r="C109" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D109" s="6">
+        <v>14351</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
+        <v>46216</v>
+      </c>
+      <c r="C110" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D110" s="6">
+        <v>11039</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
+        <v>46217</v>
+      </c>
+      <c r="C111" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D111" s="6">
+        <v>11039</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
+        <v>46218</v>
+      </c>
+      <c r="C112" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D112" s="6">
+        <v>12911</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
+        <v>46219</v>
+      </c>
+      <c r="C113" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D113" s="6">
+        <v>10759</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>46220</v>
+      </c>
+      <c r="C114" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D114" s="6">
+        <v>11835</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
+        <v>46221</v>
+      </c>
+      <c r="C115" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D115" s="6">
+        <v>13987</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
+        <v>46222</v>
+      </c>
+      <c r="C116" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D116" s="6">
+        <v>13987</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
+        <v>46223</v>
+      </c>
+      <c r="C117" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D117" s="6">
+        <v>10759</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
+        <v>46224</v>
+      </c>
+      <c r="C118" s="6">
+        <v>12143</v>
+      </c>
+      <c r="D118" s="6">
+        <v>10759</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
+        <v>46225</v>
+      </c>
+      <c r="C119" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D119" s="6">
+        <v>9055</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
+        <v>46226</v>
+      </c>
+      <c r="C120" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D120" s="6">
+        <v>9055</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
+        <v>46227</v>
+      </c>
+      <c r="C121" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D121" s="6">
+        <v>9961</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
+        <v>46228</v>
+      </c>
+      <c r="C122" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D122" s="6">
+        <v>13583</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>46229</v>
+      </c>
+      <c r="C123" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D123" s="6">
+        <v>13583</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>46230</v>
+      </c>
+      <c r="C124" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D124" s="6">
+        <v>11772</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>46231</v>
+      </c>
+      <c r="C125" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D125" s="6">
+        <v>11772</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>46232</v>
+      </c>
+      <c r="C126" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D126" s="6">
+        <v>11772</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>46233</v>
+      </c>
+      <c r="C127" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D127" s="6">
+        <v>11772</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>46234</v>
+      </c>
+      <c r="C128" s="6">
+        <v>11500</v>
+      </c>
+      <c r="D128" s="6">
+        <v>12677</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
+        <v>46265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Documents\Gearevo Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5530A-0FD5-4BC2-ACDA-350669EA5BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3D45E8-A6C9-40F3-838F-8C5BE5E50129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Current Sale Last Year</t>
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>Daily Sales Target</t>
   </si>
   <si>
     <t>Daily Sales Forecast</t>
@@ -486,11 +483,9 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
@@ -502,9 +497,7 @@
       <c r="C2" s="5">
         <v>6600</v>
       </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -516,9 +509,7 @@
       <c r="C3" s="5">
         <v>6600</v>
       </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -530,9 +521,7 @@
       <c r="C4" s="5">
         <v>6600</v>
       </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -544,9 +533,7 @@
       <c r="C5" s="5">
         <v>6600</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -558,9 +545,7 @@
       <c r="C6" s="5">
         <v>6600</v>
       </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
@@ -572,9 +557,7 @@
       <c r="C7" s="5">
         <v>6600</v>
       </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -586,9 +569,7 @@
       <c r="C8" s="5">
         <v>6600</v>
       </c>
-      <c r="D8" s="4">
-        <v>10000</v>
-      </c>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -600,9 +581,7 @@
       <c r="C9" s="5">
         <v>12572</v>
       </c>
-      <c r="D9" s="4">
-        <v>10000</v>
-      </c>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -614,9 +593,7 @@
       <c r="C10" s="5">
         <v>12572</v>
       </c>
-      <c r="D10" s="4">
-        <v>14000</v>
-      </c>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -628,9 +605,7 @@
       <c r="C11" s="5">
         <v>12572</v>
       </c>
-      <c r="D11" s="4">
-        <v>14000</v>
-      </c>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -642,9 +617,7 @@
       <c r="C12" s="5">
         <v>12572</v>
       </c>
-      <c r="D12" s="4">
-        <v>16000</v>
-      </c>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -656,9 +629,7 @@
       <c r="C13" s="5">
         <v>12572</v>
       </c>
-      <c r="D13" s="4">
-        <v>16000</v>
-      </c>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -670,9 +641,7 @@
       <c r="C14" s="5">
         <v>12572</v>
       </c>
-      <c r="D14" s="4">
-        <v>18000</v>
-      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -684,9 +653,7 @@
       <c r="C15" s="5">
         <v>12572</v>
       </c>
-      <c r="D15" s="4">
-        <v>18000</v>
-      </c>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -698,9 +665,7 @@
       <c r="C16" s="5">
         <v>11100</v>
       </c>
-      <c r="D16" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -712,9 +677,7 @@
       <c r="C17" s="5">
         <v>11100</v>
       </c>
-      <c r="D17" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -726,9 +689,7 @@
       <c r="C18" s="5">
         <v>11100</v>
       </c>
-      <c r="D18" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -740,9 +701,7 @@
       <c r="C19" s="5">
         <v>11100</v>
       </c>
-      <c r="D19" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D19" s="4"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -754,9 +713,7 @@
       <c r="C20" s="5">
         <v>11100</v>
       </c>
-      <c r="D20" s="4">
-        <v>22000</v>
-      </c>
+      <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -768,9 +725,7 @@
       <c r="C21" s="5">
         <v>11100</v>
       </c>
-      <c r="D21" s="4">
-        <v>22000</v>
-      </c>
+      <c r="D21" s="4"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -782,9 +737,7 @@
       <c r="C22" s="5">
         <v>11100</v>
       </c>
-      <c r="D22" s="4">
-        <v>10000</v>
-      </c>
+      <c r="D22" s="4"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -796,9 +749,7 @@
       <c r="C23" s="5">
         <v>16000</v>
       </c>
-      <c r="D23" s="4">
-        <v>10000</v>
-      </c>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -810,9 +761,7 @@
       <c r="C24" s="5">
         <v>16000</v>
       </c>
-      <c r="D24" s="4">
-        <v>15000</v>
-      </c>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -824,9 +773,7 @@
       <c r="C25" s="5">
         <v>16000</v>
       </c>
-      <c r="D25" s="4">
-        <v>15000</v>
-      </c>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -838,9 +785,7 @@
       <c r="C26" s="5">
         <v>16000</v>
       </c>
-      <c r="D26" s="4">
-        <v>15000</v>
-      </c>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
@@ -852,9 +797,7 @@
       <c r="C27" s="5">
         <v>16000</v>
       </c>
-      <c r="D27" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
@@ -866,9 +809,7 @@
       <c r="C28" s="5">
         <v>16000</v>
       </c>
-      <c r="D28" s="4">
-        <v>20000</v>
-      </c>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
@@ -880,9 +821,7 @@
       <c r="C29" s="5">
         <v>16000</v>
       </c>
-      <c r="D29" s="4">
-        <v>25000</v>
-      </c>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
@@ -894,9 +833,7 @@
       <c r="C30" s="5">
         <v>20000</v>
       </c>
-      <c r="D30" s="4">
-        <v>25000</v>
-      </c>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -908,9 +845,7 @@
       <c r="C31" s="5">
         <v>20000</v>
       </c>
-      <c r="D31" s="4">
-        <v>30000</v>
-      </c>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
@@ -922,9 +857,7 @@
       <c r="C32" s="5">
         <v>20000</v>
       </c>
-      <c r="D32" s="4">
-        <v>30000</v>
-      </c>
+      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
@@ -936,9 +869,7 @@
       <c r="C33" s="5">
         <v>20000</v>
       </c>
-      <c r="D33" s="4">
-        <v>30000</v>
-      </c>
+      <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -950,9 +881,7 @@
       <c r="C34" s="5">
         <v>20000</v>
       </c>
-      <c r="D34" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -964,9 +893,7 @@
       <c r="C35" s="5">
         <v>20000</v>
       </c>
-      <c r="D35" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -978,9 +905,7 @@
       <c r="C36" s="5">
         <v>20000</v>
       </c>
-      <c r="D36" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
@@ -992,9 +917,7 @@
       <c r="C37" s="5">
         <v>30000</v>
       </c>
-      <c r="D37" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
@@ -1006,9 +929,7 @@
       <c r="C38" s="5">
         <v>30000</v>
       </c>
-      <c r="D38" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
@@ -1020,9 +941,7 @@
       <c r="C39" s="5">
         <v>30000</v>
       </c>
-      <c r="D39" s="4">
-        <v>35000</v>
-      </c>
+      <c r="D39" s="4"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
@@ -1034,9 +953,7 @@
       <c r="C40" s="5">
         <v>30000</v>
       </c>
-      <c r="D40" s="4">
-        <v>38000</v>
-      </c>
+      <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
@@ -1048,9 +965,7 @@
       <c r="C41" s="5">
         <v>30000</v>
       </c>
-      <c r="D41" s="4">
-        <v>45000</v>
-      </c>
+      <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
@@ -1062,9 +977,7 @@
       <c r="C42" s="5">
         <v>30000</v>
       </c>
-      <c r="D42" s="4">
-        <v>45000</v>
-      </c>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
@@ -1076,9 +989,7 @@
       <c r="C43" s="5">
         <v>30000</v>
       </c>
-      <c r="D43" s="4">
-        <v>46000</v>
-      </c>
+      <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
@@ -1090,9 +1001,7 @@
       <c r="C44" s="5">
         <v>35000</v>
       </c>
-      <c r="D44" s="4">
-        <v>49000</v>
-      </c>
+      <c r="D44" s="4"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
@@ -1104,9 +1013,7 @@
       <c r="C45" s="5">
         <v>35000</v>
       </c>
-      <c r="D45" s="4">
-        <v>55000</v>
-      </c>
+      <c r="D45" s="4"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -1118,9 +1025,7 @@
       <c r="C46" s="5">
         <v>35000</v>
       </c>
-      <c r="D46" s="4">
-        <v>50000</v>
-      </c>
+      <c r="D46" s="4"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
@@ -1132,9 +1037,7 @@
       <c r="C47" s="5">
         <v>35000</v>
       </c>
-      <c r="D47" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D47" s="4"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
@@ -1146,9 +1049,7 @@
       <c r="C48" s="5">
         <v>35000</v>
       </c>
-      <c r="D48" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D48" s="4"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
@@ -1160,9 +1061,7 @@
       <c r="C49" s="5">
         <v>35000</v>
       </c>
-      <c r="D49" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D49" s="4"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
@@ -1174,9 +1073,7 @@
       <c r="C50" s="5">
         <v>35000</v>
       </c>
-      <c r="D50" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D50" s="4"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
@@ -1188,9 +1085,7 @@
       <c r="C51" s="5">
         <v>60000</v>
       </c>
-      <c r="D51" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D51" s="4"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
@@ -1202,9 +1097,7 @@
       <c r="C52" s="5">
         <v>60000</v>
       </c>
-      <c r="D52" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D52" s="4"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
@@ -1216,9 +1109,7 @@
       <c r="C53" s="5">
         <v>60000</v>
       </c>
-      <c r="D53" s="4">
-        <v>56000</v>
-      </c>
+      <c r="D53" s="4"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
@@ -1230,9 +1121,7 @@
       <c r="C54" s="5">
         <v>60000</v>
       </c>
-      <c r="D54" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D54" s="4"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
@@ -1244,9 +1133,7 @@
       <c r="C55" s="5">
         <v>60000</v>
       </c>
-      <c r="D55" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D55" s="4"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
@@ -1258,9 +1145,7 @@
       <c r="C56" s="5">
         <v>60000</v>
       </c>
-      <c r="D56" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D56" s="4"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
@@ -1272,9 +1157,7 @@
       <c r="C57" s="5">
         <v>60000</v>
       </c>
-      <c r="D57" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D57" s="4"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
@@ -1286,9 +1169,7 @@
       <c r="C58" s="5">
         <v>70000</v>
       </c>
-      <c r="D58" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D58" s="4"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
@@ -1300,9 +1181,7 @@
       <c r="C59" s="5">
         <v>70000</v>
       </c>
-      <c r="D59" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D59" s="4"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
@@ -1314,9 +1193,7 @@
       <c r="C60" s="5">
         <v>70000</v>
       </c>
-      <c r="D60" s="4">
-        <v>65000</v>
-      </c>
+      <c r="D60" s="4"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
@@ -1328,9 +1205,7 @@
       <c r="C61" s="5">
         <v>70000</v>
       </c>
-      <c r="D61" s="4">
-        <v>100000</v>
-      </c>
+      <c r="D61" s="4"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
@@ -1342,9 +1217,7 @@
       <c r="C62" s="5">
         <v>70000</v>
       </c>
-      <c r="D62" s="4">
-        <v>100000</v>
-      </c>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
@@ -1380,169 +1253,127 @@
       <c r="A68" s="3">
         <v>46174</v>
       </c>
-      <c r="D68" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>46175</v>
       </c>
-      <c r="D69" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>46176</v>
       </c>
-      <c r="D70" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>46177</v>
       </c>
-      <c r="D71" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>46178</v>
       </c>
-      <c r="D72" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>46179</v>
       </c>
-      <c r="D73" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>46180</v>
       </c>
-      <c r="D74" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>46181</v>
       </c>
-      <c r="D75" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>46182</v>
       </c>
-      <c r="D76" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>46183</v>
       </c>
-      <c r="D77" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>46184</v>
       </c>
-      <c r="D78" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>46185</v>
       </c>
-      <c r="D79" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>46186</v>
       </c>
-      <c r="D80" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>46187</v>
       </c>
-      <c r="D81" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>46188</v>
       </c>
-      <c r="D82" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D82" s="2"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>46189</v>
       </c>
-      <c r="D83" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>46190</v>
       </c>
-      <c r="D84" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D84" s="2"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>46191</v>
       </c>
-      <c r="D85" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D85" s="2"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>46192</v>
       </c>
-      <c r="D86" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D86" s="2"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>46193</v>
       </c>
-      <c r="D87" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D87" s="2"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>46194</v>
       </c>
-      <c r="D88" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D88" s="2"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
@@ -1551,9 +1382,7 @@
       <c r="C89" s="6">
         <v>11000</v>
       </c>
-      <c r="D89" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D89" s="2"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
@@ -1562,9 +1391,7 @@
       <c r="C90" s="6">
         <v>11000</v>
       </c>
-      <c r="D90" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D90" s="2"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
@@ -1573,9 +1400,7 @@
       <c r="C91" s="6">
         <v>12000</v>
       </c>
-      <c r="D91" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D91" s="2"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
@@ -1584,9 +1409,7 @@
       <c r="C92" s="6">
         <v>15000</v>
       </c>
-      <c r="D92" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D92" s="2"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
@@ -1595,9 +1418,7 @@
       <c r="C93" s="6">
         <v>17000</v>
       </c>
-      <c r="D93" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D93" s="2"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
@@ -1606,9 +1427,7 @@
       <c r="C94" s="6">
         <v>17500</v>
       </c>
-      <c r="D94" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D94" s="2"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
@@ -1617,9 +1436,7 @@
       <c r="C95" s="6">
         <v>16500</v>
       </c>
-      <c r="D95" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D95" s="2"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
@@ -1628,9 +1445,7 @@
       <c r="C96" s="6">
         <v>8500</v>
       </c>
-      <c r="D96" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D96" s="2"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
@@ -1639,9 +1454,7 @@
       <c r="C97" s="6">
         <v>8500</v>
       </c>
-      <c r="D97" s="2">
-        <v>12000</v>
-      </c>
+      <c r="D97" s="2"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
@@ -1650,9 +1463,7 @@
       <c r="C98" s="6">
         <v>13571</v>
       </c>
-      <c r="D98" s="6">
-        <v>10326</v>
-      </c>
+      <c r="D98" s="6"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
@@ -1661,9 +1472,7 @@
       <c r="C99" s="6">
         <v>13571</v>
       </c>
-      <c r="D99" s="6">
-        <v>10326</v>
-      </c>
+      <c r="D99" s="6"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
@@ -1672,9 +1481,7 @@
       <c r="C100" s="6">
         <v>13571</v>
       </c>
-      <c r="D100" s="6">
-        <v>11359</v>
-      </c>
+      <c r="D100" s="6"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
@@ -1683,9 +1490,7 @@
       <c r="C101" s="6">
         <v>13571</v>
       </c>
-      <c r="D101" s="6">
-        <v>13424</v>
-      </c>
+      <c r="D101" s="6"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
@@ -1694,9 +1499,7 @@
       <c r="C102" s="6">
         <v>13571</v>
       </c>
-      <c r="D102" s="6">
-        <v>13424</v>
-      </c>
+      <c r="D102" s="6"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
@@ -1705,9 +1508,7 @@
       <c r="C103" s="6">
         <v>13571</v>
       </c>
-      <c r="D103" s="6">
-        <v>10326</v>
-      </c>
+      <c r="D103" s="6"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
@@ -1716,9 +1517,7 @@
       <c r="C104" s="6">
         <v>13571</v>
       </c>
-      <c r="D104" s="6">
-        <v>25815</v>
-      </c>
+      <c r="D104" s="6"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
@@ -1727,9 +1526,7 @@
       <c r="C105" s="6">
         <v>12143</v>
       </c>
-      <c r="D105" s="6">
-        <v>11039</v>
-      </c>
+      <c r="D105" s="6"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
@@ -1738,9 +1535,7 @@
       <c r="C106" s="6">
         <v>12143</v>
       </c>
-      <c r="D106" s="6">
-        <v>11039</v>
-      </c>
+      <c r="D106" s="6"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
@@ -1749,9 +1544,7 @@
       <c r="C107" s="6">
         <v>12143</v>
       </c>
-      <c r="D107" s="6">
-        <v>12143</v>
-      </c>
+      <c r="D107" s="6"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
@@ -1760,9 +1553,7 @@
       <c r="C108" s="6">
         <v>12143</v>
       </c>
-      <c r="D108" s="6">
-        <v>14351</v>
-      </c>
+      <c r="D108" s="6"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
@@ -1771,9 +1562,7 @@
       <c r="C109" s="6">
         <v>12143</v>
       </c>
-      <c r="D109" s="6">
-        <v>14351</v>
-      </c>
+      <c r="D109" s="6"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
@@ -1782,9 +1571,7 @@
       <c r="C110" s="6">
         <v>12143</v>
       </c>
-      <c r="D110" s="6">
-        <v>11039</v>
-      </c>
+      <c r="D110" s="6"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
@@ -1793,9 +1580,7 @@
       <c r="C111" s="6">
         <v>12143</v>
       </c>
-      <c r="D111" s="6">
-        <v>11039</v>
-      </c>
+      <c r="D111" s="6"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
@@ -1804,9 +1589,7 @@
       <c r="C112" s="6">
         <v>12143</v>
       </c>
-      <c r="D112" s="6">
-        <v>12911</v>
-      </c>
+      <c r="D112" s="6"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
@@ -1815,9 +1598,7 @@
       <c r="C113" s="6">
         <v>12143</v>
       </c>
-      <c r="D113" s="6">
-        <v>10759</v>
-      </c>
+      <c r="D113" s="6"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
@@ -1826,9 +1607,7 @@
       <c r="C114" s="6">
         <v>12143</v>
       </c>
-      <c r="D114" s="6">
-        <v>11835</v>
-      </c>
+      <c r="D114" s="6"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
@@ -1837,9 +1616,7 @@
       <c r="C115" s="6">
         <v>12143</v>
       </c>
-      <c r="D115" s="6">
-        <v>13987</v>
-      </c>
+      <c r="D115" s="6"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
@@ -1848,9 +1625,7 @@
       <c r="C116" s="6">
         <v>12143</v>
       </c>
-      <c r="D116" s="6">
-        <v>13987</v>
-      </c>
+      <c r="D116" s="6"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
@@ -1859,9 +1634,7 @@
       <c r="C117" s="6">
         <v>12143</v>
       </c>
-      <c r="D117" s="6">
-        <v>10759</v>
-      </c>
+      <c r="D117" s="6"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
@@ -1870,9 +1643,7 @@
       <c r="C118" s="6">
         <v>12143</v>
       </c>
-      <c r="D118" s="6">
-        <v>10759</v>
-      </c>
+      <c r="D118" s="6"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
@@ -1881,9 +1652,7 @@
       <c r="C119" s="6">
         <v>11500</v>
       </c>
-      <c r="D119" s="6">
-        <v>9055</v>
-      </c>
+      <c r="D119" s="6"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
@@ -1892,9 +1661,7 @@
       <c r="C120" s="6">
         <v>11500</v>
       </c>
-      <c r="D120" s="6">
-        <v>9055</v>
-      </c>
+      <c r="D120" s="6"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
@@ -1903,9 +1670,7 @@
       <c r="C121" s="6">
         <v>11500</v>
       </c>
-      <c r="D121" s="6">
-        <v>9961</v>
-      </c>
+      <c r="D121" s="6"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
@@ -1914,9 +1679,7 @@
       <c r="C122" s="6">
         <v>11500</v>
       </c>
-      <c r="D122" s="6">
-        <v>13583</v>
-      </c>
+      <c r="D122" s="6"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
@@ -1925,9 +1688,7 @@
       <c r="C123" s="6">
         <v>11500</v>
       </c>
-      <c r="D123" s="6">
-        <v>13583</v>
-      </c>
+      <c r="D123" s="6"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
@@ -1936,9 +1697,7 @@
       <c r="C124" s="6">
         <v>11500</v>
       </c>
-      <c r="D124" s="6">
-        <v>11772</v>
-      </c>
+      <c r="D124" s="6"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
@@ -1947,9 +1706,7 @@
       <c r="C125" s="6">
         <v>11500</v>
       </c>
-      <c r="D125" s="6">
-        <v>11772</v>
-      </c>
+      <c r="D125" s="6"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
@@ -1958,9 +1715,7 @@
       <c r="C126" s="6">
         <v>11500</v>
       </c>
-      <c r="D126" s="6">
-        <v>11772</v>
-      </c>
+      <c r="D126" s="6"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
@@ -1969,9 +1724,7 @@
       <c r="C127" s="6">
         <v>11500</v>
       </c>
-      <c r="D127" s="6">
-        <v>11772</v>
-      </c>
+      <c r="D127" s="6"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
@@ -1980,9 +1733,7 @@
       <c r="C128" s="6">
         <v>11500</v>
       </c>
-      <c r="D128" s="6">
-        <v>12677</v>
-      </c>
+      <c r="D128" s="6"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3">

--- a/Sales_and_Target.xlsx
+++ b/Sales_and_Target.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salma\Documents\Gearevo Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3D45E8-A6C9-40F3-838F-8C5BE5E50129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82914F65-7489-499A-9A17-B295FBF1135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32B418BB-3C95-461F-AFA6-52E3F5EF10B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1735,159 +1735,252 @@
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>46235</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C129" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>46236</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C130" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>46237</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C131" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>46238</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C132" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>46239</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C133" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>46240</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C134" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>46241</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C135" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>46242</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C136" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>46243</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C137" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>46244</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C138" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>46245</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C139" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>46246</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C140" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>46247</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C141" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>46248</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C142" s="6">
+        <v>8769</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>46249</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C143" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>46250</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C144" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>46251</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C145" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>46252</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C146" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>46253</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C147" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>46254</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C148" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C149" s="6">
+        <v>7587</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>46256</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C150" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>46257</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C151" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>46258</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C152" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>46259</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C153" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>46260</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C154" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>46261</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C155" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>46262</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C156" s="6">
+        <v>9064</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>46263</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C157" s="6">
+        <v>9655</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>46264</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C158" s="6">
+        <v>9655</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>46265</v>
+      </c>
+      <c r="C159" s="6">
+        <v>9655</v>
       </c>
     </row>
   </sheetData>
